--- a/scrum/Daily Scrum.xlsx
+++ b/scrum/Daily Scrum.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="63">
   <si>
     <t>Daily Scrum</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>15 mins</t>
+  </si>
+  <si>
+    <t>Discussed Next Steps in M2</t>
   </si>
   <si>
     <t>Team Members</t>
@@ -1681,11 +1684,21 @@
       <c r="I54" s="43"/>
     </row>
     <row r="55">
-      <c r="A55" s="43"/>
-      <c r="B55" s="43"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="49"/>
+      <c r="A55" s="44">
+        <v>46056.0</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>59</v>
+      </c>
       <c r="F55" s="42"/>
       <c r="G55" s="42"/>
       <c r="H55" s="43"/>
@@ -1693,10 +1706,18 @@
     </row>
     <row r="56">
       <c r="A56" s="43"/>
-      <c r="B56" s="43"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="49"/>
+      <c r="B56" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>59</v>
+      </c>
       <c r="F56" s="42"/>
       <c r="G56" s="42"/>
       <c r="H56" s="43"/>
@@ -1704,10 +1725,18 @@
     </row>
     <row r="57">
       <c r="A57" s="43"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="49"/>
+      <c r="B57" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>59</v>
+      </c>
       <c r="F57" s="42"/>
       <c r="G57" s="42"/>
       <c r="H57" s="43"/>
@@ -1715,10 +1744,18 @@
     </row>
     <row r="58">
       <c r="A58" s="43"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="49"/>
+      <c r="B58" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>59</v>
+      </c>
       <c r="F58" s="42"/>
       <c r="G58" s="42"/>
       <c r="H58" s="43"/>
@@ -12625,14 +12662,14 @@
     <row r="2" ht="29.25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="8"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
       <c r="A3" s="51"/>
       <c r="B3" s="51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="51"/>
     </row>

--- a/scrum/Daily Scrum.xlsx
+++ b/scrum/Daily Scrum.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="64">
   <si>
     <t>Daily Scrum</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Discussed Next Steps in M2</t>
+  </si>
+  <si>
+    <t>Created Account Creation Sequence Diagram for M2</t>
   </si>
   <si>
     <t>Team Members</t>
@@ -1762,11 +1765,21 @@
       <c r="I58" s="43"/>
     </row>
     <row r="59">
-      <c r="A59" s="43"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="49"/>
+      <c r="A59" s="44">
+        <v>46057.0</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>13</v>
+      </c>
       <c r="F59" s="42"/>
       <c r="G59" s="42"/>
       <c r="H59" s="43"/>
@@ -12662,14 +12675,14 @@
     <row r="2" ht="29.25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" s="8"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
       <c r="A3" s="51"/>
       <c r="B3" s="51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="51"/>
     </row>
